--- a/Data/Changelog/Italian.xlsx
+++ b/Data/Changelog/Italian.xlsx
@@ -91,7 +91,46 @@
     <x:t>Per un compagno, ti faccio uno sconto. Non dirlo a nessuno!</x:t>
   </x:si>
   <x:si>
+    <x:t>3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026/10/15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Village\Elder\Quest</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Could you check on my son? He went to investigate the forest and hasn't returned.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Potresti controllare mio figlio? E andato a investigare nella foresta e non e ancora tornato.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Potresti controllare mio figlio? È andato a investigare nella foresta e non e ancora tornato.</x:t>
+  </x:si>
+  <x:si>
     <x:t>Pending</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Shortening</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Edited because this way it's nicer.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Village\Merchant\Wares</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Take a look at my wares! Potions, scrolls, and rare ingredients.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dai un'occhiata alla mia merce! Pozioni, pergamene e ingredienti rari.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dai un'occhiata alla mia merce!  e ingredienti rari.</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -442,18 +481,18 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J3"/>
+  <x:dimension ref="A1:J5"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="1.710625" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="6.282054" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="10.996339" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="5.139196" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="10.996339" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="10.710625" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="30.710625" style="0" customWidth="1"/>
     <x:col min="6" max="6" width="25.996339" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="64.139196" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="75.567768" style="0" customWidth="1"/>
     <x:col min="8" max="8" width="91.282054" style="0" customWidth="1"/>
-    <x:col min="9" max="9" width="55.282054" style="0" customWidth="1"/>
+    <x:col min="9" max="9" width="81.424911" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="8.853482" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -550,7 +589,71 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="J3" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:10" ht="10" customHeight="1">
+      <x:c r="A4" s="0" t="s">
         <x:v>25</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E4" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F4" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G4" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="H4" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="I4" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="J4" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:10" ht="10" customHeight="1">
+      <x:c r="A5" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E5" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="F5" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="G5" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="H5" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="I5" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="J5" s="0" t="s">
+        <x:v>18</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
